--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -550,7 +550,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-08-21 19:37:35</t>
+          <t>2026-08-22 00:38:47</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-08-21 19:37:35</t>
+          <t>2026-08-22 00:38:47</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-08-21 19:37:35</t>
+          <t>2026-08-22 00:38:47</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-08-21 19:37:35</t>
+          <t>2026-08-22 00:38:47</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-08-21 19:37:35</t>
+          <t>2026-08-22 00:38:47</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-08-21 19:37:35</t>
+          <t>2026-08-22 00:38:47</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-08-21 19:37:35</t>
+          <t>2026-08-22 00:38:47</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-08-21 19:37:35</t>
+          <t>2026-08-22 00:38:47</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-08-21 19:37:35</t>
+          <t>2026-08-22 00:38:47</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-08-21 19:37:35</t>
+          <t>2026-08-22 00:38:47</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-08-21 19:37:35</t>
+          <t>2026-08-22 00:38:47</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-08-21 19:37:35</t>
+          <t>2026-08-22 00:38:47</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-08-21 19:37:35</t>
+          <t>2026-08-22 00:38:47</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-08-21 19:37:35</t>
+          <t>2026-08-22 00:38:47</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-08-21 19:37:35</t>
+          <t>2026-08-22 00:38:47</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-08-21 19:37:35</t>
+          <t>2026-08-22 00:38:47</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-08-21 19:37:35</t>
+          <t>2026-08-22 00:38:47</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -550,7 +550,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-08-22 00:38:47</t>
+          <t>2026-08-22 11:12:30</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-08-22 00:38:47</t>
+          <t>2026-08-22 11:12:30</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-08-22 00:38:47</t>
+          <t>2026-08-22 11:12:30</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-08-22 00:38:47</t>
+          <t>2026-08-22 11:12:30</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-08-22 00:38:47</t>
+          <t>2026-08-22 11:12:30</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-08-22 00:38:47</t>
+          <t>2026-08-22 11:12:30</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-08-22 00:38:47</t>
+          <t>2026-08-22 11:12:30</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-08-22 00:38:47</t>
+          <t>2026-08-22 11:12:30</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-08-22 00:38:47</t>
+          <t>2026-08-22 11:12:30</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-08-22 00:38:47</t>
+          <t>2026-08-22 11:12:30</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-08-22 00:38:47</t>
+          <t>2026-08-22 11:12:30</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-08-22 00:38:47</t>
+          <t>2026-08-22 11:12:30</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-08-22 00:38:47</t>
+          <t>2026-08-22 11:12:30</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-08-22 00:38:47</t>
+          <t>2026-08-22 11:12:30</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-08-22 00:38:47</t>
+          <t>2026-08-22 11:12:30</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-08-22 00:38:47</t>
+          <t>2026-08-22 11:12:30</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-08-22 00:38:47</t>
+          <t>2026-08-22 11:12:30</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,35 +454,50 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>Property_Type</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Surplus_Balance_USD</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Statutory_Fee_Rate</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Est_Finder_Fee_USD</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Opportunity_Tier</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Sale_Date</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Statutory_Deadline_Window</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Clerk_Verification_URL</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
         <is>
           <t>Governing_Statute</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Enriched_Timestamp</t>
         </is>
@@ -522,57 +537,72 @@
           <t>720 S OCEAN BLVD PALM BEACH FL 33480</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Commercial / Mixed Use</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>145000</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>29000</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>2024-06-28</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>120 Days from Notice (FL Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>https://www.mypalmbeachclerk.com/</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>FL Statute § 197.582</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2026-08-22 11:12:30</t>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:56:15</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Harris</t>
+          <t>Fulton</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024-TX-04812</t>
+          <t>2024-GA-003810</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>WILLIAM &amp; MARY HOLLOWAY</t>
+          <t>MARCUS &amp; ELEANOR JENKINS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -585,60 +615,75 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>5402 BRAESVALLEY DR HOUSTON TX 77096</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>128500</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>32125</v>
-      </c>
-      <c r="K3" t="inlineStr">
+          <t>1420 PEACHTREE ST NE ATLANTA GA 30309</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>134000</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>26800</v>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2024-07-09</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>TX Tax Code § 34.04</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-08-22 11:12:30</t>
+          <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>https://www.fultonclerk.org/</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>O.C.G.A. § 48-4-5</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:56:15</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Miami-Dade</t>
+          <t>Harris</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2024-TD-004812</t>
+          <t>2024-TX-04812</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LUIS &amp; MARIA HERNANDEZ</t>
+          <t>WILLIAM &amp; MARY HOLLOWAY</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -651,65 +696,80 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>340 SW 8TH ST MIAMI FL 33130</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>112000</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>22400</v>
-      </c>
-      <c r="K4" t="inlineStr">
+          <t>5402 BRAESVALLEY DR HOUSTON TX 77096</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>128500</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>32125</v>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>FL Statute § 197.582</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-08-22 11:12:30</t>
+          <t>2 Years from Sale (TX Tax Code § 34.04)</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>TX Tax Code § 34.04</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:56:15</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hillsborough</t>
+          <t>Cobb</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2024-TD-008912</t>
+          <t>2024-GA-001550</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ROBERT &amp; CLAIRE SULLIVAN</t>
+          <t>ESTATE OF RAYMOND VAUGHN</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Individual / Estate</t>
+          <t>Estate / Deceased</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -717,65 +777,80 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4502 W SAN RAFAEL ST TAMPA FL 33629</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>92400</v>
-      </c>
-      <c r="I5" t="inlineStr">
+          <t>1205 ROSWELL RD MARIETTA GA 30062</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>118000</v>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v>18480</v>
-      </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" t="n">
+        <v>23600</v>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>2024-07-25</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>FL Statute § 197.582</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-08-22 11:12:30</t>
+          <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>https://www.cobbtax.org/</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>O.C.G.A. § 48-4-5</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:56:15</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Harris</t>
+          <t>Miami-Dade</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2024-TX-04950</t>
+          <t>2024-TD-004812</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ESTATE OF CHARLES BEAUMONT</t>
+          <t>LUIS &amp; MARIA HERNANDEZ</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Estate / Deceased</t>
+          <t>Individual / Estate</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -783,60 +858,75 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1802 HEIGHTS BLVD HOUSTON TX 77008</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>86200</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>21550</v>
-      </c>
-      <c r="K6" t="inlineStr">
+          <t>340 SW 8TH ST MIAMI FL 33130</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>112000</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>22400</v>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>2024-07-16</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>TX Tax Code § 34.04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-08-22 11:12:30</t>
+          <t>120 Days from Notice (FL Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>https://www.miamidadeclerk.gov/</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>FL Statute § 197.582</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:56:15</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Fulton</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2024-TX-02044</t>
+          <t>2024-GA-004120</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ESTATE OF MARGARET THORNTON</t>
+          <t>ESTATE OF HAROLD CRAWFORD</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -849,38 +939,53 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>6412 ABRAMS RD DALLAS TX 75231</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>77800</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>19450</v>
-      </c>
-      <c r="K7" t="inlineStr">
+          <t>892 CASCADE AVE SW ATLANTA GA 30310</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>96500</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>19300</v>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>2024-08-13</t>
-        </is>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>TX Tax Code § 34.04</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-08-22 11:12:30</t>
+          <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>https://www.fultonclerk.org/</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>O.C.G.A. § 48-4-5</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:56:15</t>
         </is>
       </c>
     </row>
@@ -892,17 +997,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Hillsborough</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2024-TD-001955</t>
+          <t>2024-TD-008912</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>JAMES &amp; LINDA CHEN</t>
+          <t>ROBERT &amp; CLAIRE SULLIVAN</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -915,60 +1020,75 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>8431 BAY BREEZE WAY ORLANDO FL 32836</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>74300</v>
-      </c>
-      <c r="I8" t="inlineStr">
+          <t>4502 W SAN RAFAEL ST TAMPA FL 33629</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>92400</v>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v>14860</v>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" t="n">
+        <v>18480</v>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>2024-08-08</t>
-        </is>
-      </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>120 Days from Notice (FL Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>https://www.hillsclerk.com/</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
           <t>FL Statute § 197.582</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2026-08-22 11:12:30</t>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:56:15</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Palm Beach</t>
+          <t>Harris</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2024-TD-004688</t>
+          <t>2024-TX-04950</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ESTATE OF ARTHUR STERLING</t>
+          <t>ESTATE OF CHARLES BEAUMONT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -981,65 +1101,80 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1410 N FEDERAL HWY LAKE WORTH FL 33460</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>68900</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>13780</v>
-      </c>
-      <c r="K9" t="inlineStr">
+          <t>1802 HEIGHTS BLVD HOUSTON TX 77008</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Commercial / Mixed Use</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>86200</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>21550</v>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>2024-07-14</t>
-        </is>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>FL Statute § 197.582</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-08-22 11:12:30</t>
+          <t>2 Years from Sale (TX Tax Code § 34.04)</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>TX Tax Code § 34.04</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:56:15</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>DeKalb</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2024-TD-001501</t>
+          <t>2024-GA-002490</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ESTATE OF ELEANOR VANCE</t>
+          <t>TERRENCE &amp; MONICA BRADLEY</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Estate / Deceased</t>
+          <t>Individual / Estate</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -1047,38 +1182,53 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3309 ROSEWOOD CT WINTER PARK FL 32792</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>61800</v>
-      </c>
-      <c r="I10" t="inlineStr">
+          <t>2340 LAVISTA RD DECATUR GA 30033</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>82400</v>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="J10" t="n">
-        <v>12360</v>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" t="n">
+        <v>16480</v>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>2024-07-03</t>
-        </is>
-      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>FL Statute § 197.582</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-08-22 11:12:30</t>
+          <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>https://www.dekalbcountytax.org/</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>O.C.G.A. § 48-4-5</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:56:15</t>
         </is>
       </c>
     </row>
@@ -1095,17 +1245,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2024-TX-01928</t>
+          <t>2024-TX-02044</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>GEORGE &amp; DOROTHY WASHINGTON</t>
+          <t>ESTATE OF MARGARET THORNTON</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Individual / Estate</t>
+          <t>Estate / Deceased</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -1113,38 +1263,53 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3819 COLONIAL AVE DALLAS TX 75215</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>59400</v>
-      </c>
-      <c r="I11" t="inlineStr">
+          <t>6412 ABRAMS RD DALLAS TX 75231</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>77800</v>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="J11" t="n">
-        <v>14850</v>
-      </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" t="n">
+        <v>19450</v>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2 Years from Sale (TX Tax Code § 34.04)</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>https://www.dallascounty.org/</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>TX Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2026-08-22 11:12:30</t>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:56:15</t>
         </is>
       </c>
     </row>
@@ -1156,22 +1321,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hillsborough</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2024-TD-009041</t>
+          <t>2024-TD-001955</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ESTATE OF HENRY PATTERSON</t>
+          <t>JAMES &amp; LINDA CHEN</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Estate / Deceased</t>
+          <t>Individual / Estate</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -1179,38 +1344,53 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>11804 N 56TH ST TEMPLE TERRACE FL 33617</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>54100</v>
-      </c>
-      <c r="I12" t="inlineStr">
+          <t>8431 BAY BREEZE WAY ORLANDO FL 32836</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>74300</v>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="J12" t="n">
-        <v>10820</v>
-      </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" t="n">
+        <v>14860</v>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>2024-08-02</t>
-        </is>
-      </c>
       <c r="M12" t="inlineStr">
         <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>120 Days from Notice (FL Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>https://www.myorangeclerk.com/</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
           <t>FL Statute § 197.582</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2026-08-22 11:12:30</t>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:56:15</t>
         </is>
       </c>
     </row>
@@ -1222,22 +1402,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Palm Beach</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2024-TD-001248</t>
+          <t>2024-TD-004688</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>RICHARD HAWKINS</t>
+          <t>ESTATE OF ARTHUR STERLING</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Individual / Estate</t>
+          <t>Estate / Deceased</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -1245,60 +1425,75 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1420 PINEWOOD DR ORLANDO FL 32808</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>48250</v>
-      </c>
-      <c r="I13" t="inlineStr">
+          <t>1410 N FEDERAL HWY LAKE WORTH FL 33460</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Commercial / Mixed Use</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>68900</v>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="J13" t="n">
-        <v>9650</v>
-      </c>
-      <c r="K13" t="inlineStr">
+      <c r="K13" t="n">
+        <v>13780</v>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>2024-06-12</t>
-        </is>
-      </c>
       <c r="M13" t="inlineStr">
         <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>120 Days from Notice (FL Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>https://www.mypalmbeachclerk.com/</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
           <t>FL Statute § 197.582</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2026-08-22 11:12:30</t>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:56:15</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Miami-Dade</t>
+          <t>Gwinnett</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2024-TD-004990</t>
+          <t>2024-GA-001920</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EUGENE FITZPATRICK</t>
+          <t>VICTORIA STRICKLAND</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1311,65 +1506,80 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1920 CORAL WAY MIAMI FL 33145</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>43500</v>
-      </c>
-      <c r="I14" t="inlineStr">
+          <t>4510 LAWRENCEVILLE HWY LILBURN GA 30047</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Commercial / Mixed Use</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>67800</v>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="J14" t="n">
-        <v>8700</v>
-      </c>
-      <c r="K14" t="inlineStr">
+      <c r="K14" t="n">
+        <v>13560</v>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>2024-08-12</t>
-        </is>
-      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>FL Statute § 197.582</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-08-22 11:12:30</t>
+          <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>https://www.gwinnetttaxcommissioner.com/</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>O.C.G.A. § 48-4-5</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:56:15</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Harris</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2024-TX-05110</t>
+          <t>2024-TD-001501</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>RAFAEL GUERRERO</t>
+          <t>ESTATE OF ELEANOR VANCE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Individual / Estate</t>
+          <t>Estate / Deceased</t>
         </is>
       </c>
       <c r="F15" t="b">
@@ -1377,60 +1587,75 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>7120 NAVIGATION BLVD HOUSTON TX 77011</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>41300</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>10325</v>
-      </c>
-      <c r="K15" t="inlineStr">
+          <t>3309 ROSEWOOD CT WINTER PARK FL 32792</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>61800</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>12360</v>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>2024-08-06</t>
-        </is>
-      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>TX Tax Code § 34.04</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-08-22 11:12:30</t>
+          <t>120 Days from Notice (FL Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>https://www.myorangeclerk.com/</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>FL Statute § 197.582</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:56:15</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hillsborough</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2024-TD-009188</t>
+          <t>2024-TX-01928</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DANIELLE KAUFMAN</t>
+          <t>GEORGE &amp; DOROTHY WASHINGTON</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1443,38 +1668,53 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2308 S ARMENIA AVE TAMPA FL 33629</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>31750</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>6350</v>
-      </c>
-      <c r="K16" t="inlineStr">
+          <t>3819 COLONIAL AVE DALLAS TX 75215</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>59400</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>14850</v>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>2024-08-10</t>
-        </is>
-      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>FL Statute § 197.582</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-08-22 11:12:30</t>
+          <t>2 Years from Sale (TX Tax Code § 34.04)</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>https://www.dallascounty.org/</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>TX Tax Code § 34.04</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:56:15</t>
         </is>
       </c>
     </row>
@@ -1486,22 +1726,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Hillsborough</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2024-TD-001622</t>
+          <t>2024-TD-009041</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MARCOS &amp; SOFIA ALVAREZ</t>
+          <t>ESTATE OF HENRY PATTERSON</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Individual / Estate</t>
+          <t>Estate / Deceased</t>
         </is>
       </c>
       <c r="F17" t="b">
@@ -1509,38 +1749,53 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>510 LAKE BREEZE DR APOPKA FL 32703</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>29400</v>
-      </c>
-      <c r="I17" t="inlineStr">
+          <t>11804 N 56TH ST TEMPLE TERRACE FL 33617</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>54100</v>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="J17" t="n">
-        <v>5880</v>
-      </c>
-      <c r="K17" t="inlineStr">
+      <c r="K17" t="n">
+        <v>10820</v>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>2024-07-17</t>
-        </is>
-      </c>
       <c r="M17" t="inlineStr">
         <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>120 Days from Notice (FL Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>https://www.hillsclerk.com/</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
           <t>FL Statute § 197.582</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2026-08-22 11:12:30</t>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:56:15</t>
         </is>
       </c>
     </row>
@@ -1557,12 +1812,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2024-TD-001844</t>
+          <t>2024-TD-001248</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>BEATRICE MONTGOMERY</t>
+          <t>RICHARD HAWKINS</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1575,38 +1830,458 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>1420 PINEWOOD DR ORLANDO FL 32808</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>48250</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>9650</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>120 Days from Notice (FL Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>https://www.myorangeclerk.com/</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>FL Statute § 197.582</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:56:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Miami-Dade</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2024-TD-004990</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>EUGENE FITZPATRICK</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="F19" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1920 CORAL WAY MIAMI FL 33145</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>43500</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>8700</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>120 Days from Notice (FL Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>https://www.miamidadeclerk.gov/</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>FL Statute § 197.582</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:56:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2024-TX-05110</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>RAFAEL GUERRERO</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="F20" t="b">
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>7120 NAVIGATION BLVD HOUSTON TX 77011</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Commercial / Mixed Use</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>41300</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>10325</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2 Years from Sale (TX Tax Code § 34.04)</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>TX Tax Code § 34.04</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:56:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Hillsborough</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2024-TD-009188</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>DANIELLE KAUFMAN</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="F21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2308 S ARMENIA AVE TAMPA FL 33629</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>31750</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>6350</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2024-08-10</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>120 Days from Notice (FL Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>https://www.hillsclerk.com/</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>FL Statute § 197.582</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:56:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2024-TD-001622</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>MARCOS &amp; SOFIA ALVAREZ</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="F22" t="b">
+        <v>1</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>510 LAKE BREEZE DR APOPKA FL 32703</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>29400</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>5880</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2024-07-17</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>120 Days from Notice (FL Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>https://www.myorangeclerk.com/</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>FL Statute § 197.582</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:56:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2024-TD-001844</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>BEATRICE MONTGOMERY</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="F23" t="b">
+        <v>1</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>220 W KALEY ST ORLANDO FL 32806</t>
         </is>
       </c>
-      <c r="H18" t="n">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
         <v>18900</v>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="J18" t="n">
+      <c r="K23" t="n">
         <v>3780</v>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>Tier 2: Medium Value ($10k-$25k)</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>2024-08-01</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>120 Days from Notice (FL Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>https://www.myorangeclerk.com/</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
         <is>
           <t>FL Statute § 197.582</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2026-08-22 11:12:30</t>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:56:15</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-08-23 12:56:15</t>
+          <t>2026-08-24 13:47:38</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-08-23 12:56:15</t>
+          <t>2026-08-24 13:47:38</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-08-23 12:56:15</t>
+          <t>2026-08-24 13:47:38</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-08-23 12:56:15</t>
+          <t>2026-08-24 13:47:38</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-08-23 12:56:15</t>
+          <t>2026-08-24 13:47:38</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-08-23 12:56:15</t>
+          <t>2026-08-24 13:47:38</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-08-23 12:56:15</t>
+          <t>2026-08-24 13:47:38</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-08-23 12:56:15</t>
+          <t>2026-08-24 13:47:38</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-08-23 12:56:15</t>
+          <t>2026-08-24 13:47:38</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-08-23 12:56:15</t>
+          <t>2026-08-24 13:47:38</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-08-23 12:56:15</t>
+          <t>2026-08-24 13:47:38</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-08-23 12:56:15</t>
+          <t>2026-08-24 13:47:38</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-08-23 12:56:15</t>
+          <t>2026-08-24 13:47:38</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-08-23 12:56:15</t>
+          <t>2026-08-24 13:47:38</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-08-23 12:56:15</t>
+          <t>2026-08-24 13:47:38</t>
         </is>
       </c>
     </row>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-08-23 12:56:15</t>
+          <t>2026-08-24 13:47:38</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-08-23 12:56:15</t>
+          <t>2026-08-24 13:47:38</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-08-23 12:56:15</t>
+          <t>2026-08-24 13:47:38</t>
         </is>
       </c>
     </row>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-08-23 12:56:15</t>
+          <t>2026-08-24 13:47:38</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-08-23 12:56:15</t>
+          <t>2026-08-24 13:47:38</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-08-23 12:56:15</t>
+          <t>2026-08-24 13:47:38</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-08-23 12:56:15</t>
+          <t>2026-08-24 13:47:38</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-08-24 13:47:38</t>
+          <t>2026-08-24 15:33:23</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-08-24 13:47:38</t>
+          <t>2026-08-24 15:33:23</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-08-24 13:47:38</t>
+          <t>2026-08-24 15:33:23</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-08-24 13:47:38</t>
+          <t>2026-08-24 15:33:23</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-08-24 13:47:38</t>
+          <t>2026-08-24 15:33:23</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-08-24 13:47:38</t>
+          <t>2026-08-24 15:33:23</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-08-24 13:47:38</t>
+          <t>2026-08-24 15:33:23</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-08-24 13:47:38</t>
+          <t>2026-08-24 15:33:23</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-08-24 13:47:38</t>
+          <t>2026-08-24 15:33:23</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-08-24 13:47:38</t>
+          <t>2026-08-24 15:33:23</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-08-24 13:47:38</t>
+          <t>2026-08-24 15:33:23</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-08-24 13:47:38</t>
+          <t>2026-08-24 15:33:23</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-08-24 13:47:38</t>
+          <t>2026-08-24 15:33:23</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-08-24 13:47:38</t>
+          <t>2026-08-24 15:33:23</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-08-24 13:47:38</t>
+          <t>2026-08-24 15:33:23</t>
         </is>
       </c>
     </row>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-08-24 13:47:38</t>
+          <t>2026-08-24 15:33:23</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-08-24 13:47:38</t>
+          <t>2026-08-24 15:33:23</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-08-24 13:47:38</t>
+          <t>2026-08-24 15:33:23</t>
         </is>
       </c>
     </row>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-08-24 13:47:38</t>
+          <t>2026-08-24 15:33:23</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-08-24 13:47:38</t>
+          <t>2026-08-24 15:33:23</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-08-24 13:47:38</t>
+          <t>2026-08-24 15:33:23</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-08-24 13:47:38</t>
+          <t>2026-08-24 15:33:23</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-08-24 15:33:23</t>
+          <t>2026-08-25 11:18:14</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-08-24 15:33:23</t>
+          <t>2026-08-25 11:18:14</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-08-24 15:33:23</t>
+          <t>2026-08-25 11:18:14</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-08-24 15:33:23</t>
+          <t>2026-08-25 11:18:14</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-08-24 15:33:23</t>
+          <t>2026-08-25 11:18:14</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-08-24 15:33:23</t>
+          <t>2026-08-25 11:18:14</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-08-24 15:33:23</t>
+          <t>2026-08-25 11:18:14</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-08-24 15:33:23</t>
+          <t>2026-08-25 11:18:14</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-08-24 15:33:23</t>
+          <t>2026-08-25 11:18:14</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-08-24 15:33:23</t>
+          <t>2026-08-25 11:18:14</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-08-24 15:33:23</t>
+          <t>2026-08-25 11:18:14</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-08-24 15:33:23</t>
+          <t>2026-08-25 11:18:14</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-08-24 15:33:23</t>
+          <t>2026-08-25 11:18:14</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-08-24 15:33:23</t>
+          <t>2026-08-25 11:18:14</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-08-24 15:33:23</t>
+          <t>2026-08-25 11:18:14</t>
         </is>
       </c>
     </row>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-08-24 15:33:23</t>
+          <t>2026-08-25 11:18:14</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-08-24 15:33:23</t>
+          <t>2026-08-25 11:18:14</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-08-24 15:33:23</t>
+          <t>2026-08-25 11:18:14</t>
         </is>
       </c>
     </row>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-08-24 15:33:23</t>
+          <t>2026-08-25 11:18:14</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-08-24 15:33:23</t>
+          <t>2026-08-25 11:18:14</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-08-24 15:33:23</t>
+          <t>2026-08-25 11:18:14</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-08-24 15:33:23</t>
+          <t>2026-08-25 11:18:14</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:R36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,55 +449,60 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Heir_Search_Recommended</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Property_Address</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Property_Type</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Surplus_Balance_USD</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Statutory_Fee_Rate</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Est_Finder_Fee_USD</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Opportunity_Tier</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Sale_Date</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Statutory_Deadline_Window</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Clerk_Verification_URL</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Governing_Statute</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Enriched_Timestamp</t>
         </is>
@@ -506,22 +511,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Palm Beach</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-TD-004501</t>
+          <t>2024-CA-008120</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ANTHONY &amp; GRACE VALENTINE</t>
+          <t>GREGORY &amp; EVELYN THATCHER</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -532,77 +537,80 @@
       <c r="F2" t="b">
         <v>1</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>720 S OCEAN BLVD PALM BEACH FL 33480</t>
-        </is>
+      <c r="G2" t="b">
+        <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>1420 WILSHIRE BLVD LOS ANGELES CA 90017</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>Commercial / Mixed Use</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>145000</v>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" t="n">
+        <v>215000</v>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>29000</v>
-      </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" t="n">
+        <v>43000</v>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2024-06-28</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>120 Days from Notice (FL Stat. § 197.582)</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>https://www.mypalmbeachclerk.com/</t>
+          <t>1 Year from Deed Recording (Cal. Rev. &amp; Tax Code § 4675)</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>FL Statute § 197.582</t>
+          <t>https://ttc.lacounty.gov/</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-08-25 11:18:14</t>
+          <t>Cal. Rev. &amp; Tax Code § 4675</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fulton</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024-GA-003810</t>
+          <t>2024-CA-005210</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MARCUS &amp; ELEANOR JENKINS</t>
+          <t>VICTOR &amp; MONICA REYES</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -613,239 +621,248 @@
       <c r="F3" t="b">
         <v>1</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1420 PEACHTREE ST NE ATLANTA GA 30309</t>
-        </is>
+      <c r="G3" t="b">
+        <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>134000</v>
-      </c>
-      <c r="J3" t="inlineStr">
+          <t>4910 LA JOLLA BLVD SAN DIEGO CA 92037</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Commercial / Mixed Use</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>184000</v>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="K3" t="n">
-        <v>26800</v>
-      </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" t="n">
+        <v>36800</v>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2024-07-02</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/</t>
+          <t>1 Year from Deed Recording (Cal. Rev. &amp; Tax Code § 4675)</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>O.C.G.A. § 48-4-5</t>
+          <t>https://www.sdttc.com/</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-08-25 11:18:14</t>
+          <t>Cal. Rev. &amp; Tax Code § 4675</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Harris</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2024-TX-04812</t>
+          <t>2024-CA-008640</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>WILLIAM &amp; MARY HOLLOWAY</t>
+          <t>ESTATE OF CAROLINE DELGADO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Individual / Estate</t>
+          <t>Estate / Deceased</t>
         </is>
       </c>
       <c r="F4" t="b">
         <v>1</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>5402 BRAESVALLEY DR HOUSTON TX 77096</t>
-        </is>
+      <c r="G4" t="b">
+        <v>1</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>128500</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>32125</v>
-      </c>
-      <c r="L4" t="inlineStr">
+          <t>3820 SUNSET BLVD LOS ANGELES CA 90026</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Commercial / Mixed Use</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>168000</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>33600</v>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2024-07-09</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2 Years from Sale (TX Tax Code § 34.04)</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/</t>
+          <t>1 Year from Deed Recording (Cal. Rev. &amp; Tax Code § 4675)</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>TX Tax Code § 34.04</t>
+          <t>https://ttc.lacounty.gov/</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-08-25 11:18:14</t>
+          <t>Cal. Rev. &amp; Tax Code § 4675</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cobb</t>
+          <t>Palm Beach</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2024-GA-001550</t>
+          <t>2024-TD-004501</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ESTATE OF RAYMOND VAUGHN</t>
+          <t>ANTHONY &amp; GRACE VALENTINE</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Estate / Deceased</t>
+          <t>Individual / Estate</t>
         </is>
       </c>
       <c r="F5" t="b">
         <v>1</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>1205 ROSWELL RD MARIETTA GA 30062</t>
-        </is>
+      <c r="G5" t="b">
+        <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>118000</v>
-      </c>
-      <c r="J5" t="inlineStr">
+          <t>720 S OCEAN BLVD PALM BEACH FL 33480</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Commercial / Mixed Use</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>145000</v>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>23600</v>
-      </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" t="n">
+        <v>29000</v>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2024-08-13</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>https://www.cobbtax.org/</t>
+          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>O.C.G.A. § 48-4-5</t>
+          <t>https://www.mypalmbeachclerk.com/</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-08-25 11:18:14</t>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Miami-Dade</t>
+          <t>Mecklenburg</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2024-TD-004812</t>
+          <t>2024-NC-003110</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LUIS &amp; MARIA HERNANDEZ</t>
+          <t>DERRICK &amp; ANGELA MORGAN</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -856,55 +873,58 @@
       <c r="F6" t="b">
         <v>1</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>340 SW 8TH ST MIAMI FL 33130</t>
-        </is>
+      <c r="G6" t="b">
+        <v>0</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>112000</v>
-      </c>
-      <c r="J6" t="inlineStr">
+          <t>5820 SHARON RD CHARLOTTE NC 28210</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Vacant Land / Acreage</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>138000</v>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="K6" t="n">
-        <v>22400</v>
-      </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" t="n">
+        <v>27600</v>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>120 Days from Notice (FL Stat. § 197.582)</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>10-Day Upset Bid / Judicial Registry (N.C.G.S. § 105-374)</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>FL Statute § 197.582</t>
+          <t>https://www.nccourts.gov/locations/mecklenburg</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-08-25 11:18:14</t>
+          <t>N.C.G.S. § 105-374</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
         </is>
       </c>
     </row>
@@ -921,93 +941,96 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2024-GA-004120</t>
+          <t>2024-GA-003810</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ESTATE OF HAROLD CRAWFORD</t>
+          <t>MARCUS &amp; ELEANOR JENKINS</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Estate / Deceased</t>
+          <t>Individual / Estate</t>
         </is>
       </c>
       <c r="F7" t="b">
         <v>1</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>892 CASCADE AVE SW ATLANTA GA 30310</t>
-        </is>
+      <c r="G7" t="b">
+        <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>1420 PEACHTREE ST NE ATLANTA GA 30309</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>96500</v>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" t="n">
+        <v>134000</v>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="K7" t="n">
-        <v>19300</v>
-      </c>
-      <c r="L7" t="inlineStr">
+      <c r="L7" t="n">
+        <v>26800</v>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2024-07-16</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr">
         <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>https://www.fultonclerk.org/</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>2026-08-25 11:18:14</t>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Hillsborough</t>
+          <t>Harris</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2024-TD-008912</t>
+          <t>2024-TX-04812</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ROBERT &amp; CLAIRE SULLIVAN</t>
+          <t>WILLIAM &amp; MARY HOLLOWAY</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1018,239 +1041,248 @@
       <c r="F8" t="b">
         <v>1</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>4502 W SAN RAFAEL ST TAMPA FL 33629</t>
-        </is>
+      <c r="G8" t="b">
+        <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>5402 BRAESVALLEY DR HOUSTON TX 77096</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>92400</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>18480</v>
-      </c>
-      <c r="L8" t="inlineStr">
+      <c r="J8" t="n">
+        <v>128500</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>32125</v>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2024-07-25</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>120 Days from Notice (FL Stat. § 197.582)</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/</t>
+          <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>FL Statute § 197.582</t>
+          <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-08-25 11:18:14</t>
+          <t>Tex. Tax Code § 34.04</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Harris</t>
+          <t>Davidson</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2024-TX-04950</t>
+          <t>2024-TN-002190</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ESTATE OF CHARLES BEAUMONT</t>
+          <t>FRANKLIN &amp; JUDITH MERCER</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Estate / Deceased</t>
+          <t>Individual / Estate</t>
         </is>
       </c>
       <c r="F9" t="b">
         <v>1</v>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>1802 HEIGHTS BLVD HOUSTON TX 77008</t>
-        </is>
+      <c r="G9" t="b">
+        <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Commercial / Mixed Use</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>86200</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>21550</v>
-      </c>
-      <c r="L9" t="inlineStr">
+          <t>2418 WEST END AVE NASHVILLE TN 37203</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>126000</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>25200</v>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2 Years from Sale (TX Tax Code § 34.04)</t>
-        </is>
-      </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/</t>
+          <t>Chancery Court Motion Procedure (T.C.A. § 67-5-2501)</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>TX Tax Code § 34.04</t>
+          <t>https://chanceryclerkandmaster.nashville.gov/</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-08-25 11:18:14</t>
+          <t>T.C.A. § 67-5-2501</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DeKalb</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2024-GA-002490</t>
+          <t>2024-CA-005780</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>TERRENCE &amp; MONICA BRADLEY</t>
+          <t>ESTATE OF DOUGLAS WINSLOW</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Individual / Estate</t>
+          <t>Estate / Deceased</t>
         </is>
       </c>
       <c r="F10" t="b">
         <v>1</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2340 LAVISTA RD DECATUR GA 30033</t>
-        </is>
+      <c r="G10" t="b">
+        <v>1</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>2104 CORONADO AVE SAN DIEGO CA 92154</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>82400</v>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" t="n">
+        <v>119500</v>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="K10" t="n">
-        <v>16480</v>
-      </c>
-      <c r="L10" t="inlineStr">
+      <c r="L10" t="n">
+        <v>23900</v>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>2024-08-06</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
-        </is>
-      </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>https://www.dekalbcountytax.org/</t>
+          <t>1 Year from Deed Recording (Cal. Rev. &amp; Tax Code § 4675)</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>O.C.G.A. § 48-4-5</t>
+          <t>https://www.sdttc.com/</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-08-25 11:18:14</t>
+          <t>Cal. Rev. &amp; Tax Code § 4675</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Cobb</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2024-TX-02044</t>
+          <t>2024-GA-001550</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ESTATE OF MARGARET THORNTON</t>
+          <t>ESTATE OF RAYMOND VAUGHN</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1261,77 +1293,80 @@
       <c r="F11" t="b">
         <v>1</v>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>6412 ABRAMS RD DALLAS TX 75231</t>
-        </is>
+      <c r="G11" t="b">
+        <v>1</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>1205 ROSWELL RD MARIETTA GA 30062</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>77800</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>19450</v>
-      </c>
-      <c r="L11" t="inlineStr">
+      <c r="J11" t="n">
+        <v>118000</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>23600</v>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>2024-08-13</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2 Years from Sale (TX Tax Code § 34.04)</t>
-        </is>
-      </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/</t>
+          <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>TX Tax Code § 34.04</t>
+          <t>https://www.cobbtax.org/</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-08-25 11:18:14</t>
+          <t>O.C.G.A. § 48-4-5</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Wake</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2024-TD-001955</t>
+          <t>2024-NC-001420</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>JAMES &amp; LINDA CHEN</t>
+          <t>HARRISON &amp; CAROLINE VANCE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1342,55 +1377,58 @@
       <c r="F12" t="b">
         <v>1</v>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>8431 BAY BREEZE WAY ORLANDO FL 32836</t>
-        </is>
+      <c r="G12" t="b">
+        <v>0</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
+          <t>4210 GLENWOOD AVE RALEIGH NC 27612</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>74300</v>
-      </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" t="n">
+        <v>114500</v>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="K12" t="n">
-        <v>14860</v>
-      </c>
-      <c r="L12" t="inlineStr">
+      <c r="L12" t="n">
+        <v>22900</v>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2024-08-08</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>120 Days from Notice (FL Stat. § 197.582)</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>10-Day Upset Bid / Judicial Registry (N.C.G.S. § 105-374)</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>FL Statute § 197.582</t>
+          <t>https://www.nccourts.gov/locations/wake</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-08-25 11:18:14</t>
+          <t>N.C.G.S. § 105-374</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
         </is>
       </c>
     </row>
@@ -1402,98 +1440,101 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Palm Beach</t>
+          <t>Miami-Dade</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2024-TD-004688</t>
+          <t>2024-TD-004812</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ESTATE OF ARTHUR STERLING</t>
+          <t>LUIS &amp; MARIA HERNANDEZ</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Estate / Deceased</t>
+          <t>Individual / Estate</t>
         </is>
       </c>
       <c r="F13" t="b">
         <v>1</v>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>1410 N FEDERAL HWY LAKE WORTH FL 33460</t>
-        </is>
+      <c r="G13" t="b">
+        <v>0</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Commercial / Mixed Use</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>68900</v>
-      </c>
-      <c r="J13" t="inlineStr">
+          <t>340 SW 8TH ST MIAMI FL 33130</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>112000</v>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="K13" t="n">
-        <v>13780</v>
-      </c>
-      <c r="L13" t="inlineStr">
+      <c r="L13" t="n">
+        <v>22400</v>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2024-07-14</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>120 Days from Notice (FL Stat. § 197.582)</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>https://www.mypalmbeachclerk.com/</t>
+          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>FL Statute § 197.582</t>
+          <t>https://www.miamidadeclerk.gov/</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-08-25 11:18:14</t>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Gwinnett</t>
+          <t>Shelby</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2024-GA-001920</t>
+          <t>2024-TN-004110</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VICTORIA STRICKLAND</t>
+          <t>LAWRENCE &amp; TINA BENNETT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1504,77 +1545,80 @@
       <c r="F14" t="b">
         <v>1</v>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>4510 LAWRENCEVILLE HWY LILBURN GA 30047</t>
-        </is>
+      <c r="G14" t="b">
+        <v>0</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Commercial / Mixed Use</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>67800</v>
-      </c>
-      <c r="J14" t="inlineStr">
+          <t>1720 POPLAR AVE MEMPHIS TN 38104</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>102000</v>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="K14" t="n">
-        <v>13560</v>
-      </c>
-      <c r="L14" t="inlineStr">
+      <c r="L14" t="n">
+        <v>20400</v>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
-        </is>
-      </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>https://www.gwinnetttaxcommissioner.com/</t>
+          <t>Chancery Court Motion Procedure (T.C.A. § 67-5-2501)</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>O.C.G.A. § 48-4-5</t>
+          <t>https://chancery.shelbycountytn.gov/</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-08-25 11:18:14</t>
+          <t>T.C.A. § 67-5-2501</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Fulton</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2024-TD-001501</t>
+          <t>2024-GA-004120</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ESTATE OF ELEANOR VANCE</t>
+          <t>ESTATE OF HAROLD CRAWFORD</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1585,136 +1629,142 @@
       <c r="F15" t="b">
         <v>1</v>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>3309 ROSEWOOD CT WINTER PARK FL 32792</t>
-        </is>
+      <c r="G15" t="b">
+        <v>1</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
+          <t>892 CASCADE AVE SW ATLANTA GA 30310</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>61800</v>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" t="n">
+        <v>96500</v>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="K15" t="n">
-        <v>12360</v>
-      </c>
-      <c r="L15" t="inlineStr">
+      <c r="L15" t="n">
+        <v>19300</v>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2024-07-03</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>120 Days from Notice (FL Stat. § 197.582)</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>FL Statute § 197.582</t>
+          <t>https://www.fultonclerk.org/</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-08-25 11:18:14</t>
+          <t>O.C.G.A. § 48-4-5</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Mecklenburg</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2024-TX-01928</t>
+          <t>2024-NC-003450</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>GEORGE &amp; DOROTHY WASHINGTON</t>
+          <t>ESTATE OF WALTER STERLING</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Individual / Estate</t>
+          <t>Estate / Deceased</t>
         </is>
       </c>
       <c r="F16" t="b">
         <v>1</v>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>3819 COLONIAL AVE DALLAS TX 75215</t>
-        </is>
+      <c r="G16" t="b">
+        <v>1</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>59400</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>14850</v>
-      </c>
-      <c r="L16" t="inlineStr">
+          <t>2910 PROVIDENCE RD CHARLOTTE NC 28211</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Vacant Land / Acreage</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>96400</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>19280</v>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2 Years from Sale (TX Tax Code § 34.04)</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/</t>
+          <t>10-Day Upset Bid / Judicial Registry (N.C.G.S. § 105-374)</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>TX Tax Code § 34.04</t>
+          <t>https://www.nccourts.gov/locations/mecklenburg</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-08-25 11:18:14</t>
+          <t>N.C.G.S. § 105-374</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
         </is>
       </c>
     </row>
@@ -1731,336 +1781,348 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2024-TD-009041</t>
+          <t>2024-TD-008912</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ESTATE OF HENRY PATTERSON</t>
+          <t>ROBERT &amp; CLAIRE SULLIVAN</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Estate / Deceased</t>
+          <t>Individual / Estate</t>
         </is>
       </c>
       <c r="F17" t="b">
         <v>1</v>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>11804 N 56TH ST TEMPLE TERRACE FL 33617</t>
-        </is>
+      <c r="G17" t="b">
+        <v>0</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
+          <t>4502 W SAN RAFAEL ST TAMPA FL 33629</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>54100</v>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" t="n">
+        <v>92400</v>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="K17" t="n">
-        <v>10820</v>
-      </c>
-      <c r="L17" t="inlineStr">
+      <c r="L17" t="n">
+        <v>18480</v>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2024-08-02</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>120 Days from Notice (FL Stat. § 197.582)</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
+          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
           <t>https://www.hillsclerk.com/</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>FL Statute § 197.582</t>
-        </is>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-08-25 11:18:14</t>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Wake</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2024-TD-001248</t>
+          <t>2024-NC-001890</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>RICHARD HAWKINS</t>
+          <t>ESTATE OF SAMUEL KAUFMAN</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Individual / Estate</t>
+          <t>Estate / Deceased</t>
         </is>
       </c>
       <c r="F18" t="b">
         <v>1</v>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>1420 PINEWOOD DR ORLANDO FL 32808</t>
-        </is>
+      <c r="G18" t="b">
+        <v>1</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
+          <t>1804 FALLS OF NEUSE RD RALEIGH NC 27609</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>48250</v>
-      </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" t="n">
+        <v>88200</v>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="K18" t="n">
-        <v>9650</v>
-      </c>
-      <c r="L18" t="inlineStr">
+      <c r="L18" t="n">
+        <v>17640</v>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2024-06-12</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>120 Days from Notice (FL Stat. § 197.582)</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>10-Day Upset Bid / Judicial Registry (N.C.G.S. § 105-374)</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>FL Statute § 197.582</t>
+          <t>https://www.nccourts.gov/locations/wake</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-08-25 11:18:14</t>
+          <t>N.C.G.S. § 105-374</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Miami-Dade</t>
+          <t>Harris</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2024-TD-004990</t>
+          <t>2024-TX-04950</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EUGENE FITZPATRICK</t>
+          <t>ESTATE OF CHARLES BEAUMONT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Individual / Estate</t>
+          <t>Estate / Deceased</t>
         </is>
       </c>
       <c r="F19" t="b">
         <v>1</v>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>1920 CORAL WAY MIAMI FL 33145</t>
-        </is>
+      <c r="G19" t="b">
+        <v>1</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>43500</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>8700</v>
-      </c>
-      <c r="L19" t="inlineStr">
+          <t>1802 HEIGHTS BLVD HOUSTON TX 77008</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Commercial / Mixed Use</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>86200</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>21550</v>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2024-08-12</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>120 Days from Notice (FL Stat. § 197.582)</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>FL Statute § 197.582</t>
+          <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-08-25 11:18:14</t>
+          <t>Tex. Tax Code § 34.04</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Harris</t>
+          <t>Davidson</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2024-TX-05110</t>
+          <t>2024-TN-002840</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>RAFAEL GUERRERO</t>
+          <t>ESTATE OF GLORIA CHANDLER</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Individual / Estate</t>
+          <t>Estate / Deceased</t>
         </is>
       </c>
       <c r="F20" t="b">
         <v>1</v>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>7120 NAVIGATION BLVD HOUSTON TX 77011</t>
-        </is>
+      <c r="G20" t="b">
+        <v>1</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Commercial / Mixed Use</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>41300</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>10325</v>
-      </c>
-      <c r="L20" t="inlineStr">
+          <t>3904 GALLATIN PIKE NASHVILLE TN 37216</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>84500</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>16900</v>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>2024-08-06</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2 Years from Sale (TX Tax Code § 34.04)</t>
-        </is>
-      </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/</t>
+          <t>Chancery Court Motion Procedure (T.C.A. § 67-5-2501)</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>TX Tax Code § 34.04</t>
+          <t>https://chanceryclerkandmaster.nashville.gov/</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-08-25 11:18:14</t>
+          <t>T.C.A. § 67-5-2501</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hillsborough</t>
+          <t>DeKalb</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2024-TD-009188</t>
+          <t>2024-GA-002490</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DANIELLE KAUFMAN</t>
+          <t>TERRENCE &amp; MONICA BRADLEY</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2071,136 +2133,142 @@
       <c r="F21" t="b">
         <v>1</v>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2308 S ARMENIA AVE TAMPA FL 33629</t>
-        </is>
+      <c r="G21" t="b">
+        <v>0</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
+          <t>2340 LAVISTA RD DECATUR GA 30033</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>31750</v>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="J21" t="n">
+        <v>82400</v>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="K21" t="n">
-        <v>6350</v>
-      </c>
-      <c r="L21" t="inlineStr">
+      <c r="L21" t="n">
+        <v>16480</v>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2024-08-10</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>120 Days from Notice (FL Stat. § 197.582)</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/</t>
+          <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>FL Statute § 197.582</t>
+          <t>https://www.dekalbcountytax.org/</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-08-25 11:18:14</t>
+          <t>O.C.G.A. § 48-4-5</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2024-TD-001622</t>
+          <t>2024-TX-02044</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MARCOS &amp; SOFIA ALVAREZ</t>
+          <t>ESTATE OF MARGARET THORNTON</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Individual / Estate</t>
+          <t>Estate / Deceased</t>
         </is>
       </c>
       <c r="F22" t="b">
         <v>1</v>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>510 LAKE BREEZE DR APOPKA FL 32703</t>
-        </is>
+      <c r="G22" t="b">
+        <v>1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
+          <t>6412 ABRAMS RD DALLAS TX 75231</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="I22" t="n">
-        <v>29400</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>5880</v>
-      </c>
-      <c r="L22" t="inlineStr">
+      <c r="J22" t="n">
+        <v>77800</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>19450</v>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2024-07-17</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>120 Days from Notice (FL Stat. § 197.582)</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>FL Statute § 197.582</t>
+          <t>https://www.dallascounty.org/</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-08-25 11:18:14</t>
+          <t>Tex. Tax Code § 34.04</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
         </is>
       </c>
     </row>
@@ -2217,71 +2285,1166 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>2024-TD-001955</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>JAMES &amp; LINDA CHEN</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="F23" t="b">
+        <v>1</v>
+      </c>
+      <c r="G23" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>8431 BAY BREEZE WAY ORLANDO FL 32836</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>74300</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>14860</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>https://www.myorangeclerk.com/</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Shelby</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2024-TN-004550</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ESTATE OF BERNARD HAYES</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Estate / Deceased</t>
+        </is>
+      </c>
+      <c r="F24" t="b">
+        <v>1</v>
+      </c>
+      <c r="G24" t="b">
+        <v>1</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>4810 PARK AVE MEMPHIS TN 38117</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>71800</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>14360</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Chancery Court Motion Procedure (T.C.A. § 67-5-2501)</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>https://chancery.shelbycountytn.gov/</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2501</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Palm Beach</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2024-TD-004688</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ESTATE OF ARTHUR STERLING</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Estate / Deceased</t>
+        </is>
+      </c>
+      <c r="F25" t="b">
+        <v>1</v>
+      </c>
+      <c r="G25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>1410 N FEDERAL HWY LAKE WORTH FL 33460</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Commercial / Mixed Use</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>68900</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>13780</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>https://www.mypalmbeachclerk.com/</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Gwinnett</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2024-GA-001920</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VICTORIA STRICKLAND</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="F26" t="b">
+        <v>1</v>
+      </c>
+      <c r="G26" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>4510 LAWRENCEVILLE HWY LILBURN GA 30047</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Commercial / Mixed Use</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>67800</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>13560</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>https://www.gwinnetttaxcommissioner.com/</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>O.C.G.A. § 48-4-5</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2024-NC-002100</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>PATRICIA HOLLOWAY</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="F27" t="b">
+        <v>1</v>
+      </c>
+      <c r="G27" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>1408 DUKE UNIVERSITY RD DURHAM NC 27701</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>64500</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>12900</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2024-07-11</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>10-Day Upset Bid / Judicial Registry (N.C.G.S. § 105-374)</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>https://www.nccourts.gov/locations/durham</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>N.C.G.S. § 105-374</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2024-TD-001501</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ESTATE OF ELEANOR VANCE</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Estate / Deceased</t>
+        </is>
+      </c>
+      <c r="F28" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>3309 ROSEWOOD CT WINTER PARK FL 32792</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>61800</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>12360</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>https://www.myorangeclerk.com/</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2024-TX-01928</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>GEORGE &amp; DOROTHY WASHINGTON</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="F29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>3819 COLONIAL AVE DALLAS TX 75215</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>59400</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>14850</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>https://www.dallascounty.org/</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Tex. Tax Code § 34.04</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Hillsborough</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2024-TD-009041</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ESTATE OF HENRY PATTERSON</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Estate / Deceased</t>
+        </is>
+      </c>
+      <c r="F30" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" t="b">
+        <v>1</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>11804 N 56TH ST TEMPLE TERRACE FL 33617</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>54100</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>10820</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>https://www.hillsclerk.com/</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2024-TD-001248</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>RICHARD HAWKINS</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="F31" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>1420 PINEWOOD DR ORLANDO FL 32808</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>48250</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>9650</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>https://www.myorangeclerk.com/</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Miami-Dade</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2024-TD-004990</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>EUGENE FITZPATRICK</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="F32" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>1920 CORAL WAY MIAMI FL 33145</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>43500</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>8700</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>https://www.miamidadeclerk.gov/</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2024-TX-05110</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>RAFAEL GUERRERO</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="F33" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" t="b">
+        <v>0</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>7120 NAVIGATION BLVD HOUSTON TX 77011</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Commercial / Mixed Use</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>41300</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>10325</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>https://www.hcdistrictclerk.com/</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Tex. Tax Code § 34.04</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Hillsborough</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2024-TD-009188</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>DANIELLE KAUFMAN</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="F34" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2308 S ARMENIA AVE TAMPA FL 33629</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>31750</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>6350</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2024-08-10</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>https://www.hillsclerk.com/</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2024-TD-001622</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>MARCOS &amp; SOFIA ALVAREZ</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="F35" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>510 LAKE BREEZE DR APOPKA FL 32703</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>29400</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>5880</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>2024-07-17</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>https://www.myorangeclerk.com/</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>2024-TD-001844</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>BEATRICE MONTGOMERY</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F23" t="b">
-        <v>1</v>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="F36" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" t="inlineStr">
         <is>
           <t>220 W KALEY ST ORLANDO FL 32806</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="I23" t="n">
+      <c r="J36" t="n">
         <v>18900</v>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="K23" t="n">
+      <c r="L36" t="n">
         <v>3780</v>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>Tier 2: Medium Value ($10k-$25k)</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>2024-08-01</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>120 Days from Notice (FL Stat. § 197.582)</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
         <is>
           <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>FL Statute § 197.582</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>2026-08-25 11:18:14</t>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R36"/>
+  <dimension ref="A1:T36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,20 +489,30 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>Days_Remaining_To_Claim</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Claim_Urgency_Tier</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Statutory_Deadline_Window</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Clerk_Verification_URL</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Governing_Statute</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Enriched_Timestamp</t>
         </is>
@@ -571,24 +581,32 @@
           <t>2024-07-09</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" t="n">
+        <v>306</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>1 Year from Deed Recording (Cal. Rev. &amp; Tax Code § 4675)</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>https://ttc.lacounty.gov/</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Cal. Rev. &amp; Tax Code § 4675</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -655,24 +673,32 @@
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" t="n">
+        <v>313</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>1 Year from Deed Recording (Cal. Rev. &amp; Tax Code § 4675)</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>https://www.sdttc.com/</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>Cal. Rev. &amp; Tax Code § 4675</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -739,24 +765,32 @@
           <t>2024-07-30</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O4" t="n">
+        <v>327</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>1 Year from Deed Recording (Cal. Rev. &amp; Tax Code § 4675)</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>https://ttc.lacounty.gov/</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Cal. Rev. &amp; Tax Code § 4675</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -823,24 +857,32 @@
           <t>2024-06-28</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O5" t="n">
+        <v>40</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tier 1: High Urgency (&lt; 45 Days)</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>https://www.mypalmbeachclerk.com/</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -907,24 +949,32 @@
           <t>2024-07-25</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O6" t="n">
+        <v>322</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>10-Day Upset Bid / Judicial Registry (N.C.G.S. § 105-374)</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>https://www.nccourts.gov/locations/mecklenburg</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>N.C.G.S. § 105-374</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -991,24 +1041,32 @@
           <t>2024-07-02</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O7" t="n">
+        <v>1029</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>https://www.fultonclerk.org/</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -1075,24 +1133,32 @@
           <t>2024-07-09</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O8" t="n">
+        <v>671</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -1159,24 +1225,32 @@
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O9" t="n">
+        <v>313</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Chancery Court Motion Procedure (T.C.A. § 67-5-2501)</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>https://chanceryclerkandmaster.nashville.gov/</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>T.C.A. § 67-5-2501</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -1243,24 +1317,32 @@
           <t>2024-08-06</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O10" t="n">
+        <v>334</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>1 Year from Deed Recording (Cal. Rev. &amp; Tax Code § 4675)</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>https://www.sdttc.com/</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>Cal. Rev. &amp; Tax Code § 4675</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -1327,24 +1409,32 @@
           <t>2024-08-13</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O11" t="n">
+        <v>1071</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>https://www.cobbtax.org/</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -1411,24 +1501,32 @@
           <t>2024-07-18</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O12" t="n">
+        <v>315</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>10-Day Upset Bid / Judicial Registry (N.C.G.S. § 105-374)</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>https://www.nccourts.gov/locations/wake</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>N.C.G.S. § 105-374</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -1495,24 +1593,32 @@
           <t>2024-08-05</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O13" t="n">
+        <v>78</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>https://www.miamidadeclerk.gov/</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1685,32 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O14" t="n">
+        <v>320</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>Chancery Court Motion Procedure (T.C.A. § 67-5-2501)</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>https://chancery.shelbycountytn.gov/</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>T.C.A. § 67-5-2501</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -1663,24 +1777,32 @@
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O15" t="n">
+        <v>1043</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>https://www.fultonclerk.org/</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -1747,24 +1869,32 @@
           <t>2024-08-08</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="O16" t="n">
+        <v>336</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>10-Day Upset Bid / Judicial Registry (N.C.G.S. § 105-374)</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>https://www.nccourts.gov/locations/mecklenburg</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>N.C.G.S. § 105-374</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -1831,24 +1961,32 @@
           <t>2024-07-25</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O17" t="n">
+        <v>67</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>https://www.hillsclerk.com/</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -1915,24 +2053,32 @@
           <t>2024-08-01</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="O18" t="n">
+        <v>329</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>10-Day Upset Bid / Judicial Registry (N.C.G.S. § 105-374)</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>https://www.nccourts.gov/locations/wake</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>N.C.G.S. § 105-374</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -1999,24 +2145,32 @@
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="O19" t="n">
+        <v>678</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -2083,24 +2237,32 @@
           <t>2024-08-06</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="O20" t="n">
+        <v>334</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>Chancery Court Motion Procedure (T.C.A. § 67-5-2501)</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>https://chanceryclerkandmaster.nashville.gov/</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>T.C.A. § 67-5-2501</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -2167,24 +2329,32 @@
           <t>2024-08-06</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="O21" t="n">
+        <v>1064</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>https://www.dekalbcountytax.org/</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -2251,24 +2421,32 @@
           <t>2024-08-13</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="O22" t="n">
+        <v>706</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
         <is>
           <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>https://www.dallascounty.org/</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -2335,24 +2513,32 @@
           <t>2024-08-08</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="O23" t="n">
+        <v>81</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
         <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -2419,24 +2605,32 @@
           <t>2024-08-13</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="O24" t="n">
+        <v>341</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
         <is>
           <t>Chancery Court Motion Procedure (T.C.A. § 67-5-2501)</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>https://chancery.shelbycountytn.gov/</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>T.C.A. § 67-5-2501</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -2503,24 +2697,32 @@
           <t>2024-07-14</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="O25" t="n">
+        <v>56</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
         <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>https://www.mypalmbeachclerk.com/</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -2587,24 +2789,32 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="O26" t="n">
+        <v>1050</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
         <is>
           <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>https://www.gwinnetttaxcommissioner.com/</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -2671,24 +2881,32 @@
           <t>2024-07-11</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="O27" t="n">
+        <v>308</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
         <is>
           <t>10-Day Upset Bid / Judicial Registry (N.C.G.S. § 105-374)</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>https://www.nccourts.gov/locations/durham</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>N.C.G.S. § 105-374</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -2755,24 +2973,32 @@
           <t>2024-07-03</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="O28" t="n">
+        <v>45</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Tier 1: High Urgency (&lt; 45 Days)</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
         <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -2839,24 +3065,32 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="O29" t="n">
+        <v>685</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
         <is>
           <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>https://www.dallascounty.org/</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -2923,24 +3157,32 @@
           <t>2024-08-02</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="O30" t="n">
+        <v>75</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
         <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>https://www.hillsclerk.com/</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -3007,24 +3249,32 @@
           <t>2024-06-12</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="O31" t="n">
+        <v>24</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Tier 1: High Urgency (&lt; 45 Days)</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
         <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -3091,24 +3341,32 @@
           <t>2024-08-12</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="O32" t="n">
+        <v>85</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
         <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>https://www.miamidadeclerk.gov/</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -3175,24 +3433,32 @@
           <t>2024-08-06</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="O33" t="n">
+        <v>699</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
         <is>
           <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -3259,24 +3525,32 @@
           <t>2024-08-10</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="O34" t="n">
+        <v>83</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
         <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>https://www.hillsclerk.com/</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -3343,24 +3617,32 @@
           <t>2024-07-17</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="O35" t="n">
+        <v>59</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
         <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -3427,24 +3709,32 @@
           <t>2024-08-01</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="O36" t="n">
+        <v>74</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
         <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2790,7 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
         </is>
       </c>
       <c r="O27" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -3618,7 +3618,7 @@
         </is>
       </c>
       <c r="O35" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2790,7 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
         </is>
       </c>
       <c r="O27" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -3618,7 +3618,7 @@
         </is>
       </c>
       <c r="O35" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2790,7 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
         </is>
       </c>
       <c r="O27" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -3618,7 +3618,7 @@
         </is>
       </c>
       <c r="O35" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2790,7 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
         </is>
       </c>
       <c r="O27" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -3618,7 +3618,7 @@
         </is>
       </c>
       <c r="O35" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2790,7 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
         </is>
       </c>
       <c r="O27" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -3618,7 +3618,7 @@
         </is>
       </c>
       <c r="O35" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:40</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:40</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:40</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:39</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:40</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:39</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:39</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:40</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:40</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:39</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:40</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:39</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:40</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:39</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:40</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:39</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:40</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:39</t>
         </is>
       </c>
     </row>
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:40</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:39</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:39</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:39</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:40</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:39</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2790,7 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:39</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
         </is>
       </c>
       <c r="O27" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:40</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:39</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:39</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:39</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:39</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:39</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:39</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:39</t>
         </is>
       </c>
     </row>
@@ -3618,7 +3618,7 @@
         </is>
       </c>
       <c r="O35" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:39</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:39</t>
         </is>
       </c>
     </row>
